--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99327</v>
+        <v>99330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 48370-2025 artfynd.xlsx
+++ b/artfynd/A 48370-2025 artfynd.xlsx
@@ -2862,7 +2862,7 @@
         <v>136151572</v>
       </c>
       <c r="B21" t="n">
-        <v>99331</v>
+        <v>99336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
